--- a/output/laminas_comunales/comunal_s_fonasa_a_2024_arica_y_parinacota.xlsx
+++ b/output/laminas_comunales/comunal_s_fonasa_a_2024_arica_y_parinacota.xlsx
@@ -375,31 +375,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>15101</t>
+          <t>15201</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Arica</t>
+          <t>Putre</t>
         </is>
       </c>
       <c r="C2">
-        <v>219927</v>
+        <v>93.293142426526</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>15201</t>
+          <t>15202</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Putre</t>
+          <t>General Lagos</t>
         </is>
       </c>
       <c r="C3">
-        <v>1238</v>
+        <v>92.38845144356955</v>
       </c>
     </row>
     <row r="4">
@@ -414,22 +414,22 @@
         </is>
       </c>
       <c r="C4">
-        <v>539</v>
+        <v>92.13675213675214</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>15202</t>
+          <t>15101</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>General Lagos</t>
+          <t>Arica</t>
         </is>
       </c>
       <c r="C5">
-        <v>352</v>
+        <v>86.98749337489024</v>
       </c>
     </row>
   </sheetData>
@@ -485,7 +485,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a FONASA</t>
+          <t>Porcentaje de residentes afiliados a FONASA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/output/laminas_comunales/comunal_s_fonasa_a_2024_arica_y_parinacota.xlsx
+++ b/output/laminas_comunales/comunal_s_fonasa_a_2024_arica_y_parinacota.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C119"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -375,16 +375,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>15201</t>
+          <t>15202</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Putre</t>
+          <t>General Lagos</t>
         </is>
       </c>
       <c r="C2">
-        <v>93.293142426526</v>
+        <v>1206.824146981627</v>
       </c>
     </row>
     <row r="3">
@@ -399,37 +399,1747 @@
         </is>
       </c>
       <c r="C3">
-        <v>92.38845144356955</v>
+        <v>673.7532808398951</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>15102</t>
+          <t>15202</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>General Lagos</t>
         </is>
       </c>
       <c r="C4">
-        <v>92.13675213675214</v>
+        <v>475.3280839895013</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>15101</t>
+          <t>15201</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Arica</t>
+          <t>Putre</t>
         </is>
       </c>
       <c r="C5">
+        <v>93.293142426526</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>15202</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>General Lagos</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>92.38845144356955</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>15102</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Camarones</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>92.13675213675214</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C8">
         <v>86.98749337489024</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>15202</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>General Lagos</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>58.79265091863517</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>15202</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>General Lagos</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>52.23097112860892</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>15102</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Camarones</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>49.05982905982906</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>15201</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Putre</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>47.85229841748304</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>15202</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>General Lagos</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>47.50656167979002</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>15201</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Putre</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>45.44084400904296</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>45.15516600349648</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>15202</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>General Lagos</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>44.61942257217848</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>15102</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Camarones</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>44.61538461538461</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>15102</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Camarones</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>43.07692307692308</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>41.83232737139377</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>15202</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>General Lagos</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>40.15748031496063</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>15202</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>General Lagos</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>36.74540682414698</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>15201</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Putre</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>35.34287867370008</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>35.27406200311677</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>15202</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>General Lagos</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>33.85826771653543</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>15201</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Putre</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>32.02712886209495</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>15201</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Putre</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>27.80708364732479</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>15102</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Camarones</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>27.52136752136752</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>15202</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>General Lagos</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>23.35958005249344</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>15102</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Camarones</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>22.90598290598291</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>20.52478779872323</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>15202</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>General Lagos</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>20.20997375328084</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>19.37458963872387</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>15201</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Putre</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>18.31198191409194</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>15202</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>General Lagos</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>18.11023622047244</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>15201</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Putre</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>17.93519216277317</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>15201</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Putre</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>16.95553880934439</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>15102</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Camarones</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>16.92307692307692</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>15102</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Camarones</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>16.75213675213675</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>16.35195747272828</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>15202</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>General Lagos</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>15.74803149606299</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>15102</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Camarones</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>15.04273504273504</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>15202</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>General Lagos</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>14.96062992125984</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>15102</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Camarones</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>14.18803418803419</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>13.85379668230324</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>15202</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>General Lagos</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>13.38582677165354</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>12.48961736530262</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>12.46944538931914</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>15201</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Putre</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>12.35870384325546</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>15102</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Camarones</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>12.30769230769231</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>11.99164642876919</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>15201</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Putre</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>11.83119819140919</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>11.81405393432637</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>15201</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Putre</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>11.68048229088169</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>15202</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>General Lagos</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>11.28608923884515</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>15202</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>General Lagos</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>11.02362204724409</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>15201</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Putre</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>10.85154483798041</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>10.58791421768331</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>15201</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Putre</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>10.32403918613414</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>15102</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Camarones</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>10.08547008547009</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>15102</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Camarones</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>9.914529914529915</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>15102</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Camarones</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>9.743589743589743</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>15102</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Camarones</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>9.572649572649572</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>15102</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Camarones</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>9.572649572649572</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>15201</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Putre</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>9.344385832705351</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>9.24311581878446</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>15202</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>General Lagos</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>9.186351706036746</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>15202</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>General Lagos</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>9.186351706036746</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>15201</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Putre</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>8.967596081386587</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>15102</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Camarones</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>8.547008547008547</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>15201</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Putre</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>7.987942727957799</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>15102</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Camarones</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>7.863247863247863</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>15202</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>General Lagos</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>6.824146981627297</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>6.656356545608443</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>15201</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Putre</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>4.822908816880181</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>4.018969568003291</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>15201</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Putre</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>3.918613413715147</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>15102</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Camarones</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>3.247863247863248</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>2.637386977605151</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>15102</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Camarones</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>1.709401709401709</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>15201</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Putre</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>1.582516955538809</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>1.484024586078963</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>15102</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Camarones</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>1.367521367521368</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>15201</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Putre</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>1.356443104747551</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>15201</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Putre</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>1.356443104747551</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>1.281513768362431</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>15201</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Putre</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>1.055011303692539</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>15201</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Putre</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>0.9042954031650339</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>0.8618575621178202</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>15102</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Camarones</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>0.8547008547008547</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>0.8484095781288317</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>0.8329839494355802</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>15202</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>General Lagos</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>0.7874015748031497</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>0.7222358459968516</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>15102</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Camarones</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>0.6837606837606838</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>15102</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Camarones</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>0.6837606837606838</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>0.6253312554879641</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>15102</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Camarones</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>0.5128205128205128</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>15102</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Camarones</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>0.5128205128205128</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>15201</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Putre</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>0.4521477015825169</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>15201</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Putre</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>0.4521477015825169</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>15201</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Putre</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>0.3767897513187641</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>15102</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Camarones</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>0.3418803418803419</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>15102</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Camarones</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>0.3418803418803419</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>15201</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Putre</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>0.3014318010550113</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>15202</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>General Lagos</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>0.2624671916010499</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>15202</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>General Lagos</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>0.2624671916010499</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>15202</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>General Lagos</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>0.2624671916010499</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>15202</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>General Lagos</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>0.2624671916010499</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>15102</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Camarones</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>0.1709401709401709</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>15201</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Putre</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>0.1507159005275057</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>0.1443680634111998</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>15201</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Putre</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>0.07535795026375283</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>0.06723991994494237</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>0.03757524938099721</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>0.02412726539200873</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>0.0177988023383671</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>0.01265692610728327</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>0.00355976046767342</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>15101</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>0.003164231526820817</v>
       </c>
     </row>
   </sheetData>
